--- a/metas.xlsx
+++ b/metas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/Liquidacióncvs/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/02 Febrero/Liquidacióncvs - liquidación/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="514" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{212945BE-825C-4D35-AD01-AE528E1CC2B2}"/>
+  <xr:revisionPtr revIDLastSave="586" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0CA9870-9B81-4CF3-A2CF-8623E5EE38BE}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D1391136-BBFC-43C7-B899-B77B0ECC5956}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$B$1:$E$133</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$B$1:$E$121</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="35">
   <si>
     <t>BARBOSA</t>
   </si>
@@ -132,9 +132,6 @@
   </si>
   <si>
     <t>OTROS</t>
-  </si>
-  <si>
-    <t>FOCO</t>
   </si>
   <si>
     <t>GENERAL</t>
@@ -549,7 +546,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}">
-  <dimension ref="A1:E277"/>
+  <dimension ref="A1:E253"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
@@ -560,7 +557,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>23</v>
@@ -577,7 +574,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>5</v>
@@ -594,7 +591,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>5</v>
@@ -611,7 +608,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>5</v>
@@ -628,7 +625,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>5</v>
@@ -645,16 +642,16 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D6" s="3">
-        <v>29</v>
+        <v>146</v>
       </c>
       <c r="E6" s="3">
         <v>2800</v>
@@ -662,33 +659,33 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D7" s="3">
-        <v>146</v>
+        <v>1500</v>
       </c>
       <c r="E7" s="3">
-        <v>2800</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D8" s="3">
-        <v>1500</v>
+        <v>37</v>
       </c>
       <c r="E8" s="3">
         <v>2400</v>
@@ -696,16 +693,16 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D9" s="3">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="E9" s="3">
         <v>2400</v>
@@ -713,16 +710,16 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="3">
-        <v>6</v>
+        <v>29</v>
+      </c>
+      <c r="D10">
+        <v>82</v>
       </c>
       <c r="E10" s="3">
         <v>2400</v>
@@ -730,16 +727,16 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D11">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="E11" s="3">
         <v>2400</v>
@@ -747,50 +744,50 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="3">
         <v>0</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D12">
-        <v>25</v>
-      </c>
       <c r="E12" s="3">
-        <v>2400</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>0</v>
+        <v>33</v>
+      </c>
+      <c r="B13" t="s">
+        <v>2</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D13">
-        <v>95</v>
+        <v>12</v>
       </c>
       <c r="E13" s="3">
-        <v>2400</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s">
         <v>2</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E14" s="3">
         <v>1350</v>
@@ -798,16 +795,16 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B15" t="s">
         <v>2</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D15">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="E15" s="3">
         <v>1350</v>
@@ -815,16 +812,16 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B16" t="s">
         <v>2</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D16" s="3">
-        <v>4</v>
+        <v>30</v>
+      </c>
+      <c r="D16">
+        <v>32</v>
       </c>
       <c r="E16" s="3">
         <v>1350</v>
@@ -832,67 +829,67 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B17" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D17">
-        <v>50</v>
+        <v>22</v>
+      </c>
+      <c r="D17" s="3">
+        <v>800</v>
       </c>
       <c r="E17" s="3">
-        <v>1350</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B18" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D18">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E18" s="3">
-        <v>1350</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B19" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D19">
-        <v>32</v>
+        <v>28</v>
+      </c>
+      <c r="D19" s="3">
+        <v>1</v>
       </c>
       <c r="E19" s="3">
-        <v>1350</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B20" t="s">
         <v>3</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D20" s="3">
-        <v>800</v>
+        <v>29</v>
+      </c>
+      <c r="D20">
+        <v>65</v>
       </c>
       <c r="E20" s="3">
         <v>1700</v>
@@ -900,16 +897,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B21" t="s">
         <v>3</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D21">
-        <v>33</v>
+        <v>135</v>
       </c>
       <c r="E21" s="3">
         <v>1700</v>
@@ -917,84 +914,84 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B22" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D22" s="3">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="E22" s="3">
-        <v>1700</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B23" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D23">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="E23" s="3">
-        <v>1700</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B24" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D24">
-        <v>20</v>
+        <v>28</v>
+      </c>
+      <c r="D24" s="3">
+        <v>1</v>
       </c>
       <c r="E24" s="3">
-        <v>1700</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B25" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D25">
-        <v>135</v>
+        <v>50</v>
       </c>
       <c r="E25" s="3">
-        <v>1700</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B26" t="s">
         <v>8</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D26" s="3">
-        <v>1200</v>
+        <v>30</v>
+      </c>
+      <c r="D26">
+        <v>69</v>
       </c>
       <c r="E26" s="3">
         <v>1450</v>
@@ -1002,129 +999,129 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D27">
-        <v>18</v>
+        <v>22</v>
+      </c>
+      <c r="D27" s="3">
+        <v>1200</v>
       </c>
       <c r="E27" s="3">
-        <v>1450</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D28" s="3">
-        <v>1</v>
+        <v>27</v>
+      </c>
+      <c r="D28">
+        <v>37</v>
       </c>
       <c r="E28" s="3">
-        <v>1450</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B29" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D29">
-        <v>50</v>
+        <v>28</v>
+      </c>
+      <c r="D29" s="3">
+        <v>1</v>
       </c>
       <c r="E29" s="3">
-        <v>1450</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B30" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D30">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="E30" s="3">
-        <v>1450</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B31" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D31">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E31" s="3">
-        <v>1450</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D32" s="3">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="E32" s="3">
-        <v>1500</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D33">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E33" s="3">
-        <v>1500</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>28</v>
@@ -1133,310 +1130,310 @@
         <v>1</v>
       </c>
       <c r="E34" s="3">
-        <v>1500</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D35">
-        <v>45</v>
+        <v>160</v>
       </c>
       <c r="E35" s="3">
-        <v>1500</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D36">
-        <v>14</v>
+        <v>176</v>
       </c>
       <c r="E36" s="3">
-        <v>1500</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B37" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D37">
-        <v>68</v>
+        <v>22</v>
+      </c>
+      <c r="D37" s="3">
+        <v>1500</v>
       </c>
       <c r="E37" s="3">
-        <v>1500</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B38" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D38" s="3">
-        <v>1500</v>
+        <v>27</v>
+      </c>
+      <c r="D38">
+        <v>26</v>
       </c>
       <c r="E38" s="3">
-        <v>4000</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B39" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D39">
-        <v>42</v>
+        <v>28</v>
+      </c>
+      <c r="D39" s="3">
+        <v>1</v>
       </c>
       <c r="E39" s="3">
-        <v>4000</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B40" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D40" s="3">
-        <v>1</v>
+        <v>29</v>
+      </c>
+      <c r="D40">
+        <v>140</v>
       </c>
       <c r="E40" s="3">
-        <v>4000</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B41" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D41">
-        <v>160</v>
+        <v>98</v>
       </c>
       <c r="E41" s="3">
-        <v>4000</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B42" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D42">
-        <v>48</v>
+        <v>22</v>
+      </c>
+      <c r="D42" s="3">
+        <v>1200</v>
       </c>
       <c r="E42" s="3">
-        <v>4000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B43" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D43">
-        <v>176</v>
+        <v>32</v>
       </c>
       <c r="E43" s="3">
-        <v>4000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B44" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D44" s="3">
-        <v>1500</v>
+        <v>6</v>
       </c>
       <c r="E44" s="3">
-        <v>2600</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B45" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D45">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="E45" s="3">
-        <v>2600</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B46" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D46" s="3">
-        <v>1</v>
+        <v>30</v>
+      </c>
+      <c r="D46">
+        <v>128</v>
       </c>
       <c r="E46" s="3">
-        <v>2600</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>34</v>
-      </c>
-      <c r="B47" t="s">
-        <v>13</v>
+        <v>33</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D47">
-        <v>140</v>
+        <v>22</v>
+      </c>
+      <c r="D47" s="3">
+        <v>1200</v>
       </c>
       <c r="E47" s="3">
-        <v>2600</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B48" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D48">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="E48" s="3">
-        <v>2600</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B49" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D49">
-        <v>98</v>
+        <v>28</v>
+      </c>
+      <c r="D49" s="3">
+        <v>6</v>
       </c>
       <c r="E49" s="3">
-        <v>2600</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B50" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D50" s="3">
-        <v>1200</v>
+        <v>29</v>
+      </c>
+      <c r="D50">
+        <v>25</v>
       </c>
       <c r="E50" s="3">
-        <v>2000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B51" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D51">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="E51" s="3">
-        <v>2000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B52" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D52" s="3">
-        <v>6</v>
+        <v>800</v>
       </c>
       <c r="E52" s="3">
         <v>2000</v>
@@ -1444,16 +1441,16 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B53" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D53">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="E53" s="3">
         <v>2000</v>
@@ -1461,16 +1458,16 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B54" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D54">
-        <v>17</v>
+        <v>28</v>
+      </c>
+      <c r="D54" s="3">
+        <v>1</v>
       </c>
       <c r="E54" s="3">
         <v>2000</v>
@@ -1478,16 +1475,16 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B55" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D55">
-        <v>128</v>
+        <v>82</v>
       </c>
       <c r="E55" s="3">
         <v>2000</v>
@@ -1495,146 +1492,146 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>34</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>12</v>
+        <v>33</v>
+      </c>
+      <c r="B56" t="s">
+        <v>17</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D56" s="3">
-        <v>1200</v>
+        <v>30</v>
+      </c>
+      <c r="D56">
+        <v>60</v>
       </c>
       <c r="E56" s="3">
-        <v>1500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B57" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D57">
-        <v>17</v>
+        <v>22</v>
+      </c>
+      <c r="D57" s="3">
+        <v>1200</v>
       </c>
       <c r="E57" s="3">
-        <v>1500</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B58" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D58" s="3">
-        <v>6</v>
+        <v>27</v>
+      </c>
+      <c r="D58">
+        <v>16</v>
       </c>
       <c r="E58" s="3">
-        <v>1500</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B59" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D59">
-        <v>25</v>
+        <v>28</v>
+      </c>
+      <c r="D59" s="3">
+        <v>4</v>
       </c>
       <c r="E59" s="3">
-        <v>1500</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B60" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D60">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E60" s="3">
-        <v>1500</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B61" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D61">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="E61" s="3">
-        <v>1500</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B62" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D62" s="3">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="E62" s="3">
-        <v>2000</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B63" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D63">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="E63" s="3">
-        <v>2000</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B64" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>28</v>
@@ -1643,174 +1640,174 @@
         <v>1</v>
       </c>
       <c r="E64" s="3">
-        <v>2000</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B65" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D65">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="E65" s="3">
-        <v>2000</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B66" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D66">
-        <v>25</v>
+        <v>183</v>
       </c>
       <c r="E66" s="3">
-        <v>2000</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B67" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D67">
-        <v>60</v>
+        <v>22</v>
+      </c>
+      <c r="D67" s="3">
+        <v>1200</v>
       </c>
       <c r="E67" s="3">
-        <v>2000</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B68" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C68" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D68">
         <v>22</v>
       </c>
-      <c r="D68" s="3">
-        <v>1200</v>
-      </c>
       <c r="E68" s="3">
-        <v>1100</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B69" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D69">
-        <v>16</v>
+        <v>28</v>
+      </c>
+      <c r="D69" s="3">
+        <v>6</v>
       </c>
       <c r="E69" s="3">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B70" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D70" s="3">
-        <v>4</v>
+        <v>29</v>
+      </c>
+      <c r="D70">
+        <v>60</v>
       </c>
       <c r="E70" s="3">
-        <v>1100</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B71" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D71">
-        <v>30</v>
+        <v>168</v>
       </c>
       <c r="E71" s="3">
-        <v>1100</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B72" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D72">
-        <v>9</v>
+        <v>22</v>
+      </c>
+      <c r="D72" s="3">
+        <v>1200</v>
       </c>
       <c r="E72" s="3">
-        <v>1100</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B73" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D73">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="E73" s="3">
-        <v>1100</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B74" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D74" s="3">
-        <v>1200</v>
+        <v>1</v>
       </c>
       <c r="E74" s="3">
         <v>2200</v>
@@ -1818,16 +1815,16 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B75" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D75">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="E75" s="3">
         <v>2200</v>
@@ -1835,16 +1832,16 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B76" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D76" s="3">
-        <v>1</v>
+        <v>30</v>
+      </c>
+      <c r="D76">
+        <v>92</v>
       </c>
       <c r="E76" s="3">
         <v>2200</v>
@@ -1852,265 +1849,265 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B77" t="s">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D77">
-        <v>60</v>
+        <v>22</v>
+      </c>
+      <c r="D77" s="3">
+        <v>1500</v>
       </c>
       <c r="E77" s="3">
-        <v>2200</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B78" t="s">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D78">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="E78" s="3">
-        <v>2200</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B79" t="s">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D79">
-        <v>183</v>
+        <v>28</v>
+      </c>
+      <c r="D79" s="3">
+        <v>10</v>
       </c>
       <c r="E79" s="3">
-        <v>2200</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B80" t="s">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D80" s="3">
-        <v>1200</v>
+        <v>29</v>
+      </c>
+      <c r="D80">
+        <v>102</v>
       </c>
       <c r="E80" s="3">
-        <v>1600</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B81" t="s">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D81">
-        <v>22</v>
+        <v>129</v>
       </c>
       <c r="E81" s="3">
-        <v>1600</v>
+        <v>2850</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B82" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C82" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D82">
+        <v>1500</v>
+      </c>
+      <c r="E82" s="3">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>33</v>
+      </c>
+      <c r="B83" t="s">
+        <v>4</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D83">
+        <v>62</v>
+      </c>
+      <c r="E83" s="3">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>33</v>
+      </c>
+      <c r="B84" t="s">
+        <v>4</v>
+      </c>
+      <c r="C84" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D82" s="3">
-        <v>6</v>
-      </c>
-      <c r="E82" s="3">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>34</v>
-      </c>
-      <c r="B83" t="s">
-        <v>21</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D83">
-        <v>60</v>
-      </c>
-      <c r="E83" s="3">
-        <v>1600</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>34</v>
-      </c>
-      <c r="B84" t="s">
-        <v>21</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="D84">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E84" s="3">
-        <v>1600</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B85" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D85">
-        <v>168</v>
+        <v>124</v>
       </c>
       <c r="E85" s="3">
-        <v>1600</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B86" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D86" s="3">
-        <v>1200</v>
+        <v>30</v>
+      </c>
+      <c r="D86">
+        <v>183</v>
       </c>
       <c r="E86" s="3">
-        <v>2200</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B87" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D87">
-        <v>23</v>
+        <v>22</v>
+      </c>
+      <c r="D87" s="3">
+        <v>1500</v>
       </c>
       <c r="E87" s="3">
-        <v>2200</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B88" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D88" s="3">
-        <v>1</v>
+        <v>27</v>
+      </c>
+      <c r="D88">
+        <v>78</v>
       </c>
       <c r="E88" s="3">
-        <v>2200</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B89" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D89">
-        <v>72</v>
+        <v>28</v>
+      </c>
+      <c r="D89" s="3">
+        <v>16</v>
       </c>
       <c r="E89" s="3">
-        <v>2200</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B90" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D90">
-        <v>22</v>
+        <v>96</v>
       </c>
       <c r="E90" s="3">
-        <v>2200</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B91" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C91" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D91">
-        <v>92</v>
+        <v>198</v>
       </c>
       <c r="E91" s="3">
-        <v>2200</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B92" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C92" s="3" t="s">
         <v>22</v>
@@ -2119,32 +2116,32 @@
         <v>1500</v>
       </c>
       <c r="E92" s="3">
-        <v>2850</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B93" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C93" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D93">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="E93" s="3">
-        <v>2850</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B94" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C94" s="3" t="s">
         <v>28</v>
@@ -2153,395 +2150,395 @@
         <v>10</v>
       </c>
       <c r="E94" s="3">
-        <v>2850</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B95" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C95" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D95">
-        <v>102</v>
+        <v>72</v>
       </c>
       <c r="E95" s="3">
-        <v>2850</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B96" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D96">
-        <v>31</v>
+        <v>151</v>
       </c>
       <c r="E96" s="3">
-        <v>2850</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B97" t="s">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D97">
-        <v>129</v>
+        <v>22</v>
+      </c>
+      <c r="D97" s="3">
+        <v>1500</v>
       </c>
       <c r="E97" s="3">
-        <v>2850</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B98" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D98">
-        <v>1500</v>
+        <v>103</v>
       </c>
       <c r="E98" s="3">
-        <v>3500</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B99" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D99">
-        <v>62</v>
+        <v>28</v>
+      </c>
+      <c r="D99" s="3">
+        <v>14</v>
       </c>
       <c r="E99" s="3">
-        <v>3500</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B100" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D100">
-        <v>10</v>
+        <v>236</v>
       </c>
       <c r="E100" s="3">
-        <v>3500</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B101" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D101">
-        <v>124</v>
+        <v>192</v>
       </c>
       <c r="E101" s="3">
-        <v>3500</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B102" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D102">
-        <v>37</v>
+        <v>22</v>
+      </c>
+      <c r="D102" s="3">
+        <v>1500</v>
       </c>
       <c r="E102" s="3">
-        <v>3500</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B103" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D103">
-        <v>183</v>
+        <v>62</v>
       </c>
       <c r="E103" s="3">
-        <v>3500</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B104" t="s">
+        <v>19</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D104" s="3">
         <v>11</v>
       </c>
-      <c r="C104" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D104" s="3">
-        <v>1500</v>
-      </c>
       <c r="E104" s="3">
-        <v>3500</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B105" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D105">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E105" s="3">
-        <v>3500</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B106" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D106" s="3">
-        <v>16</v>
+        <v>30</v>
+      </c>
+      <c r="D106">
+        <v>181</v>
       </c>
       <c r="E106" s="3">
-        <v>3500</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B107" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D107">
-        <v>96</v>
+        <v>22</v>
+      </c>
+      <c r="D107" s="3">
+        <v>1500</v>
       </c>
       <c r="E107" s="3">
-        <v>3500</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B108" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D108">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E108" s="3">
-        <v>3500</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B109" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D109">
-        <v>198</v>
+        <v>28</v>
+      </c>
+      <c r="D109" s="3">
+        <v>10</v>
       </c>
       <c r="E109" s="3">
-        <v>3500</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B110" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D110" s="3">
-        <v>1500</v>
+        <v>29</v>
+      </c>
+      <c r="D110">
+        <v>92</v>
       </c>
       <c r="E110" s="3">
-        <v>2300</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B111" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D111">
-        <v>44</v>
+        <v>126</v>
       </c>
       <c r="E111" s="3">
-        <v>2300</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B112" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D112" s="3">
-        <v>10</v>
+        <v>22</v>
+      </c>
+      <c r="D112">
+        <v>27700</v>
       </c>
       <c r="E112" s="3">
-        <v>2300</v>
+        <v>53500</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B113" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D113">
-        <v>72</v>
+        <v>840</v>
       </c>
       <c r="E113" s="3">
-        <v>2300</v>
+        <v>53500</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B114" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D114">
-        <v>22</v>
+        <v>131</v>
       </c>
       <c r="E114" s="3">
-        <v>2300</v>
+        <v>53500</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B115" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D115">
-        <v>151</v>
+        <v>2433</v>
       </c>
       <c r="E115" s="3">
-        <v>2300</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B116" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D116" s="3">
-        <v>1500</v>
+        <v>30</v>
+      </c>
+      <c r="D116">
+        <v>2738</v>
       </c>
       <c r="E116" s="3">
-        <v>5700</v>
+        <v>53500</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
+        <v>33</v>
+      </c>
+      <c r="B117" t="s">
         <v>34</v>
       </c>
-      <c r="B117" t="s">
-        <v>16</v>
-      </c>
       <c r="C117" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D117">
-        <v>103</v>
+        <v>22</v>
+      </c>
+      <c r="D117" s="3">
+        <v>1500</v>
       </c>
       <c r="E117" s="3">
         <v>5700</v>
@@ -2549,16 +2546,16 @@
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
+        <v>33</v>
+      </c>
+      <c r="B118" t="s">
         <v>34</v>
       </c>
-      <c r="B118" t="s">
-        <v>16</v>
-      </c>
       <c r="C118" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D118" s="3">
-        <v>14</v>
+        <v>27</v>
+      </c>
+      <c r="D118">
+        <v>103</v>
       </c>
       <c r="E118" s="3">
         <v>5700</v>
@@ -2566,16 +2563,16 @@
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
+        <v>33</v>
+      </c>
+      <c r="B119" t="s">
         <v>34</v>
       </c>
-      <c r="B119" t="s">
-        <v>16</v>
-      </c>
       <c r="C119" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D119">
-        <v>236</v>
+        <v>28</v>
+      </c>
+      <c r="D119" s="3">
+        <v>14</v>
       </c>
       <c r="E119" s="3">
         <v>5700</v>
@@ -2583,27 +2580,27 @@
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
+        <v>33</v>
+      </c>
+      <c r="B120" t="s">
         <v>34</v>
       </c>
-      <c r="B120" t="s">
-        <v>16</v>
-      </c>
       <c r="C120" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D120">
-        <v>71</v>
+        <v>2433</v>
       </c>
       <c r="E120" s="3">
-        <v>5700</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
+        <v>33</v>
+      </c>
+      <c r="B121" t="s">
         <v>34</v>
-      </c>
-      <c r="B121" t="s">
-        <v>16</v>
       </c>
       <c r="C121" s="3" t="s">
         <v>30</v>
@@ -2616,551 +2613,248 @@
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
-        <v>34</v>
-      </c>
-      <c r="B122" t="s">
-        <v>19</v>
-      </c>
-      <c r="C122" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D122" s="3">
-        <v>1500</v>
-      </c>
-      <c r="E122" s="3">
-        <v>2600</v>
-      </c>
+      <c r="B122" s="3"/>
+      <c r="C122" s="3"/>
+      <c r="D122" s="3"/>
+      <c r="E122" s="3"/>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
-        <v>34</v>
-      </c>
-      <c r="B123" t="s">
-        <v>19</v>
-      </c>
-      <c r="C123" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D123">
-        <v>62</v>
-      </c>
-      <c r="E123" s="3">
-        <v>2600</v>
-      </c>
+      <c r="B123" s="3"/>
+      <c r="C123" s="3"/>
+      <c r="D123" s="3"/>
+      <c r="E123" s="3"/>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
-        <v>34</v>
-      </c>
-      <c r="B124" t="s">
-        <v>19</v>
-      </c>
-      <c r="C124" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D124" s="3">
-        <v>11</v>
-      </c>
-      <c r="E124" s="3">
-        <v>2600</v>
-      </c>
+      <c r="B124" s="3"/>
+      <c r="C124" s="3"/>
+      <c r="D124" s="3"/>
+      <c r="E124" s="3"/>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
-        <v>34</v>
-      </c>
-      <c r="B125" t="s">
-        <v>19</v>
-      </c>
-      <c r="C125" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D125">
-        <v>74</v>
-      </c>
-      <c r="E125" s="3">
-        <v>2600</v>
-      </c>
+      <c r="B125" s="3"/>
+      <c r="C125" s="3"/>
+      <c r="E125" s="3"/>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
-        <v>34</v>
-      </c>
-      <c r="B126" t="s">
-        <v>19</v>
-      </c>
-      <c r="C126" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D126">
-        <v>22</v>
-      </c>
-      <c r="E126" s="3">
-        <v>2600</v>
-      </c>
+      <c r="B126" s="3"/>
+      <c r="C126" s="3"/>
+      <c r="E126" s="3"/>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
-        <v>34</v>
-      </c>
-      <c r="B127" t="s">
-        <v>19</v>
-      </c>
-      <c r="C127" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D127">
-        <v>181</v>
-      </c>
-      <c r="E127" s="3">
-        <v>2600</v>
-      </c>
+      <c r="B127" s="3"/>
+      <c r="C127" s="3"/>
+      <c r="E127" s="3"/>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
-        <v>34</v>
-      </c>
-      <c r="B128" t="s">
-        <v>15</v>
-      </c>
-      <c r="C128" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D128" s="3">
-        <v>1500</v>
-      </c>
-      <c r="E128" s="3">
-        <v>2650</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
-        <v>34</v>
-      </c>
-      <c r="B129" t="s">
-        <v>15</v>
-      </c>
-      <c r="C129" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D129">
-        <v>30</v>
-      </c>
-      <c r="E129" s="3">
-        <v>2650</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
-        <v>34</v>
-      </c>
-      <c r="B130" t="s">
-        <v>15</v>
-      </c>
-      <c r="C130" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D130" s="3">
-        <v>10</v>
-      </c>
-      <c r="E130" s="3">
-        <v>2650</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
-        <v>34</v>
-      </c>
-      <c r="B131" t="s">
-        <v>15</v>
-      </c>
-      <c r="C131" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D131">
-        <v>92</v>
-      </c>
-      <c r="E131" s="3">
-        <v>2650</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
-        <v>34</v>
-      </c>
-      <c r="B132" t="s">
-        <v>15</v>
-      </c>
-      <c r="C132" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D132">
-        <v>28</v>
-      </c>
-      <c r="E132" s="3">
-        <v>2650</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
-        <v>34</v>
-      </c>
-      <c r="B133" t="s">
-        <v>15</v>
-      </c>
-      <c r="C133" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D133">
-        <v>126</v>
-      </c>
-      <c r="E133" s="3">
-        <v>2650</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
-        <v>34</v>
-      </c>
-      <c r="B134" t="s">
-        <v>32</v>
-      </c>
-      <c r="C134" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D134">
-        <v>27700</v>
-      </c>
-      <c r="E134" s="3">
-        <v>53500</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
-        <v>34</v>
-      </c>
-      <c r="B135" t="s">
-        <v>32</v>
-      </c>
-      <c r="C135" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D135">
-        <v>840</v>
-      </c>
-      <c r="E135" s="3">
-        <v>53500</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A136" t="s">
-        <v>34</v>
-      </c>
-      <c r="B136" t="s">
-        <v>32</v>
-      </c>
-      <c r="C136" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D136">
-        <v>131</v>
-      </c>
-      <c r="E136" s="3">
-        <v>53500</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
-        <v>34</v>
-      </c>
-      <c r="B137" t="s">
-        <v>32</v>
-      </c>
-      <c r="C137" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D137">
-        <v>1868</v>
-      </c>
-      <c r="E137" s="3">
-        <v>53500</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
-        <v>34</v>
-      </c>
-      <c r="B138" t="s">
-        <v>32</v>
-      </c>
-      <c r="C138" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D138">
-        <v>565</v>
-      </c>
-      <c r="E138" s="3">
-        <v>53500</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A139" t="s">
-        <v>34</v>
-      </c>
-      <c r="B139" t="s">
-        <v>32</v>
-      </c>
-      <c r="C139" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D139">
-        <v>2738</v>
-      </c>
-      <c r="E139" s="3">
-        <v>53500</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
-        <v>34</v>
-      </c>
-      <c r="B140" t="s">
-        <v>35</v>
-      </c>
-      <c r="C140" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D140" s="3">
-        <v>1500</v>
-      </c>
-      <c r="E140" s="3">
-        <v>5700</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
-        <v>34</v>
-      </c>
-      <c r="B141" t="s">
-        <v>35</v>
-      </c>
-      <c r="C141" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D141">
-        <v>103</v>
-      </c>
-      <c r="E141" s="3">
-        <v>5700</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A142" t="s">
-        <v>34</v>
-      </c>
-      <c r="B142" t="s">
-        <v>35</v>
-      </c>
-      <c r="C142" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D142" s="3">
-        <v>14</v>
-      </c>
-      <c r="E142" s="3">
-        <v>5700</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A143" t="s">
-        <v>34</v>
-      </c>
-      <c r="B143" t="s">
-        <v>35</v>
-      </c>
-      <c r="C143" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D143">
-        <v>236</v>
-      </c>
-      <c r="E143" s="3">
-        <v>5700</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
-        <v>34</v>
-      </c>
-      <c r="B144" t="s">
-        <v>35</v>
-      </c>
-      <c r="C144" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D144">
-        <v>71</v>
-      </c>
-      <c r="E144" s="3">
-        <v>5700</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
-        <v>34</v>
-      </c>
-      <c r="B145" t="s">
-        <v>35</v>
-      </c>
-      <c r="C145" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D145">
-        <v>192</v>
-      </c>
-      <c r="E145" s="3">
-        <v>5700</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B146" s="3"/>
+      <c r="C128" s="3"/>
+      <c r="D128" s="3"/>
+      <c r="E128" s="3"/>
+    </row>
+    <row r="129" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C129" s="3"/>
+      <c r="E129" s="3"/>
+    </row>
+    <row r="130" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C130" s="3"/>
+      <c r="D130" s="3"/>
+      <c r="E130" s="3"/>
+    </row>
+    <row r="131" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C131" s="3"/>
+      <c r="E131" s="3"/>
+    </row>
+    <row r="132" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C132" s="3"/>
+      <c r="E132" s="3"/>
+    </row>
+    <row r="133" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C133" s="3"/>
+      <c r="E133" s="3"/>
+    </row>
+    <row r="134" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C134" s="3"/>
+      <c r="D134" s="3"/>
+      <c r="E134" s="3"/>
+    </row>
+    <row r="135" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C135" s="3"/>
+      <c r="E135" s="3"/>
+    </row>
+    <row r="136" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C136" s="3"/>
+      <c r="D136" s="3"/>
+      <c r="E136" s="3"/>
+    </row>
+    <row r="137" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C137" s="3"/>
+      <c r="E137" s="3"/>
+    </row>
+    <row r="138" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C138" s="3"/>
+      <c r="E138" s="3"/>
+    </row>
+    <row r="139" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C139" s="3"/>
+      <c r="E139" s="3"/>
+    </row>
+    <row r="140" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C140" s="3"/>
+      <c r="D140" s="3"/>
+      <c r="E140" s="3"/>
+    </row>
+    <row r="141" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C141" s="3"/>
+      <c r="E141" s="3"/>
+    </row>
+    <row r="142" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C142" s="3"/>
+      <c r="D142" s="3"/>
+      <c r="E142" s="3"/>
+    </row>
+    <row r="143" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C143" s="3"/>
+      <c r="E143" s="3"/>
+    </row>
+    <row r="144" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C144" s="3"/>
+      <c r="E144" s="3"/>
+    </row>
+    <row r="145" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C145" s="3"/>
+      <c r="E145" s="3"/>
+    </row>
+    <row r="146" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C146" s="3"/>
       <c r="D146" s="3"/>
       <c r="E146" s="3"/>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B147" s="3"/>
+    <row r="147" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C147" s="3"/>
-      <c r="D147" s="3"/>
       <c r="E147" s="3"/>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B148" s="3"/>
+    <row r="148" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C148" s="3"/>
       <c r="D148" s="3"/>
       <c r="E148" s="3"/>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B149" s="3"/>
+    <row r="149" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C149" s="3"/>
       <c r="E149" s="3"/>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B150" s="3"/>
+    <row r="150" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C150" s="3"/>
       <c r="E150" s="3"/>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B151" s="3"/>
+    <row r="151" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C151" s="3"/>
       <c r="E151" s="3"/>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="152" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C152" s="3"/>
       <c r="D152" s="3"/>
       <c r="E152" s="3"/>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="153" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C153" s="3"/>
       <c r="E153" s="3"/>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="154" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C154" s="3"/>
       <c r="D154" s="3"/>
       <c r="E154" s="3"/>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="155" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C155" s="3"/>
       <c r="E155" s="3"/>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="156" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C156" s="3"/>
       <c r="E156" s="3"/>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="157" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C157" s="3"/>
       <c r="E157" s="3"/>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="158" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C158" s="3"/>
       <c r="D158" s="3"/>
       <c r="E158" s="3"/>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="159" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C159" s="3"/>
       <c r="E159" s="3"/>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="160" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C160" s="3"/>
       <c r="D160" s="3"/>
       <c r="E160" s="3"/>
     </row>
-    <row r="161" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="161" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C161" s="3"/>
       <c r="E161" s="3"/>
     </row>
-    <row r="162" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C162" s="3"/>
       <c r="E162" s="3"/>
     </row>
-    <row r="163" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="163" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C163" s="3"/>
       <c r="E163" s="3"/>
     </row>
-    <row r="164" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="164" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C164" s="3"/>
       <c r="D164" s="3"/>
       <c r="E164" s="3"/>
     </row>
-    <row r="165" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="165" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C165" s="3"/>
       <c r="E165" s="3"/>
     </row>
-    <row r="166" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="166" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C166" s="3"/>
       <c r="D166" s="3"/>
       <c r="E166" s="3"/>
     </row>
-    <row r="167" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="167" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C167" s="3"/>
       <c r="E167" s="3"/>
     </row>
-    <row r="168" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="168" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C168" s="3"/>
       <c r="E168" s="3"/>
     </row>
-    <row r="169" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="169" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C169" s="3"/>
       <c r="E169" s="3"/>
     </row>
-    <row r="170" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="170" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B170" s="1"/>
       <c r="C170" s="3"/>
       <c r="D170" s="3"/>
       <c r="E170" s="3"/>
     </row>
-    <row r="171" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="171" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C171" s="3"/>
       <c r="E171" s="3"/>
     </row>
-    <row r="172" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="172" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C172" s="3"/>
       <c r="D172" s="3"/>
       <c r="E172" s="3"/>
     </row>
-    <row r="173" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="173" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C173" s="3"/>
       <c r="E173" s="3"/>
     </row>
-    <row r="174" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C174" s="3"/>
       <c r="E174" s="3"/>
     </row>
-    <row r="175" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="175" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C175" s="3"/>
       <c r="E175" s="3"/>
     </row>
-    <row r="176" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="176" spans="2:5" x14ac:dyDescent="0.25">
       <c r="C176" s="3"/>
       <c r="D176" s="3"/>
       <c r="E176" s="3"/>
@@ -3234,73 +2928,72 @@
       <c r="C192" s="3"/>
       <c r="E192" s="3"/>
     </row>
-    <row r="193" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="193" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C193" s="3"/>
       <c r="E193" s="3"/>
     </row>
-    <row r="194" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B194" s="1"/>
+    <row r="194" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C194" s="3"/>
       <c r="D194" s="3"/>
       <c r="E194" s="3"/>
     </row>
-    <row r="195" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="195" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C195" s="3"/>
       <c r="E195" s="3"/>
     </row>
-    <row r="196" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="196" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C196" s="3"/>
       <c r="D196" s="3"/>
       <c r="E196" s="3"/>
     </row>
-    <row r="197" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="197" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C197" s="3"/>
       <c r="E197" s="3"/>
     </row>
-    <row r="198" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="198" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C198" s="3"/>
       <c r="E198" s="3"/>
     </row>
-    <row r="199" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="199" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C199" s="3"/>
       <c r="E199" s="3"/>
     </row>
-    <row r="200" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="200" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C200" s="3"/>
       <c r="D200" s="3"/>
       <c r="E200" s="3"/>
     </row>
-    <row r="201" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="201" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C201" s="3"/>
       <c r="E201" s="3"/>
     </row>
-    <row r="202" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="202" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C202" s="3"/>
       <c r="D202" s="3"/>
       <c r="E202" s="3"/>
     </row>
-    <row r="203" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="203" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C203" s="3"/>
       <c r="E203" s="3"/>
     </row>
-    <row r="204" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="204" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C204" s="3"/>
       <c r="E204" s="3"/>
     </row>
-    <row r="205" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="205" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C205" s="3"/>
       <c r="E205" s="3"/>
     </row>
-    <row r="206" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="206" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C206" s="3"/>
       <c r="D206" s="3"/>
       <c r="E206" s="3"/>
     </row>
-    <row r="207" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="207" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C207" s="3"/>
       <c r="E207" s="3"/>
     </row>
-    <row r="208" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="208" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C208" s="3"/>
       <c r="D208" s="3"/>
       <c r="E208" s="3"/>
@@ -3319,7 +3012,6 @@
     </row>
     <row r="212" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C212" s="3"/>
-      <c r="D212" s="3"/>
       <c r="E212" s="3"/>
     </row>
     <row r="213" spans="3:5" x14ac:dyDescent="0.25">
@@ -3328,7 +3020,6 @@
     </row>
     <row r="214" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C214" s="3"/>
-      <c r="D214" s="3"/>
       <c r="E214" s="3"/>
     </row>
     <row r="215" spans="3:5" x14ac:dyDescent="0.25">
@@ -3423,6 +3114,7 @@
     </row>
     <row r="236" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C236" s="3"/>
+      <c r="D236" s="3"/>
       <c r="E236" s="3"/>
     </row>
     <row r="237" spans="3:5" x14ac:dyDescent="0.25">
@@ -3431,6 +3123,7 @@
     </row>
     <row r="238" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C238" s="3"/>
+      <c r="D238" s="3"/>
       <c r="E238" s="3"/>
     </row>
     <row r="239" spans="3:5" x14ac:dyDescent="0.25">
@@ -3473,7 +3166,6 @@
     </row>
     <row r="248" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C248" s="3"/>
-      <c r="D248" s="3"/>
       <c r="E248" s="3"/>
     </row>
     <row r="249" spans="3:5" x14ac:dyDescent="0.25">
@@ -3482,7 +3174,6 @@
     </row>
     <row r="250" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C250" s="3"/>
-      <c r="D250" s="3"/>
       <c r="E250" s="3"/>
     </row>
     <row r="251" spans="3:5" x14ac:dyDescent="0.25">
@@ -3497,110 +3188,8 @@
       <c r="C253" s="3"/>
       <c r="E253" s="3"/>
     </row>
-    <row r="254" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C254" s="3"/>
-      <c r="D254" s="3"/>
-      <c r="E254" s="3"/>
-    </row>
-    <row r="255" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C255" s="3"/>
-      <c r="E255" s="3"/>
-    </row>
-    <row r="256" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C256" s="3"/>
-      <c r="D256" s="3"/>
-      <c r="E256" s="3"/>
-    </row>
-    <row r="257" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C257" s="3"/>
-      <c r="E257" s="3"/>
-    </row>
-    <row r="258" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C258" s="3"/>
-      <c r="E258" s="3"/>
-    </row>
-    <row r="259" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C259" s="3"/>
-      <c r="E259" s="3"/>
-    </row>
-    <row r="260" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C260" s="3"/>
-      <c r="D260" s="3"/>
-      <c r="E260" s="3"/>
-    </row>
-    <row r="261" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C261" s="3"/>
-      <c r="E261" s="3"/>
-    </row>
-    <row r="262" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C262" s="3"/>
-      <c r="D262" s="3"/>
-      <c r="E262" s="3"/>
-    </row>
-    <row r="263" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C263" s="3"/>
-      <c r="E263" s="3"/>
-    </row>
-    <row r="264" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C264" s="3"/>
-      <c r="E264" s="3"/>
-    </row>
-    <row r="265" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C265" s="3"/>
-      <c r="E265" s="3"/>
-    </row>
-    <row r="266" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C266" s="3"/>
-      <c r="D266" s="3"/>
-      <c r="E266" s="3"/>
-    </row>
-    <row r="267" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C267" s="3"/>
-      <c r="E267" s="3"/>
-    </row>
-    <row r="268" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C268" s="3"/>
-      <c r="D268" s="3"/>
-      <c r="E268" s="3"/>
-    </row>
-    <row r="269" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C269" s="3"/>
-      <c r="E269" s="3"/>
-    </row>
-    <row r="270" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C270" s="3"/>
-      <c r="E270" s="3"/>
-    </row>
-    <row r="271" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C271" s="3"/>
-      <c r="E271" s="3"/>
-    </row>
-    <row r="272" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C272" s="3"/>
-      <c r="E272" s="3"/>
-    </row>
-    <row r="273" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C273" s="3"/>
-      <c r="E273" s="3"/>
-    </row>
-    <row r="274" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C274" s="3"/>
-      <c r="E274" s="3"/>
-    </row>
-    <row r="275" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C275" s="3"/>
-      <c r="E275" s="3"/>
-    </row>
-    <row r="276" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C276" s="3"/>
-      <c r="E276" s="3"/>
-    </row>
-    <row r="277" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C277" s="3"/>
-      <c r="E277" s="3"/>
-    </row>
   </sheetData>
-  <autoFilter ref="B1:E133" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}"/>
+  <autoFilter ref="B1:E121" xr:uid="{6956BB2C-DA9E-4412-BCD4-BB80A11153FE}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>